--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T01:57:53+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:09:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -1901,18 +1901,18 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Civic Center Drive</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>2</v>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1927,18 +1927,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Civic Center Drive</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>McKelvey Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>3</v>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, unclassified</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2109,18 +2109,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>McKelvey Road</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
+      <c r="D23" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential, service, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>3</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -2187,14 +2187,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2213,18 +2213,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Crest Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Struble Road</t>
+          <t>Houston Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>tertiary, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Houston Road</t>
+          <t>Sevenhills Drive</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2291,18 +2291,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Sevenhills Drive</t>
+          <t>Crest Road</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>0</v>
+      <c r="D30" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2317,18 +2317,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Struble Road</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>3</v>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>tertiary, unclassified</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -63025,12 +63025,14 @@
           <t>Blue Ash / Montgomery</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1934</v>
+      </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Blue Ash, Montgomery, Deer Park, Silverton, Kenwood, Madeira</t>
@@ -63043,12 +63045,14 @@
           <t>Springdale / Sharonville</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1549</v>
+      </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Springdale, Sharonville, Glendale, Evendale, Lincoln Heights</t>
@@ -63081,12 +63085,14 @@
           <t>Forest Park / Pleasant Run</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>NOT STARTED</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>AUDIT COMPLETE</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2066</v>
+      </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Forest Park, Pleasant Run, Greenhills</t>
@@ -63290,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T01:57:53+00:00</t>
+          <t>2026-04-29T02:09:54+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:09:54+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:18:35+00:00</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>McKelvey Road</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
+      <c r="D21" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>residential, service, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2083,14 +2083,14 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -2109,18 +2109,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>McKelvey Road</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>3</v>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, unclassified</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2213,18 +2213,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Crest Road</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sevenhills Drive</t>
+          <t>Struble Road</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary, unclassified</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2291,18 +2291,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Crest Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Struble Road</t>
+          <t>Sevenhills Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>tertiary, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:09:54+00:00</t>
+          <t>2026-04-29T02:18:35+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:18:35+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:34:03+00:00</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>McKelvey Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>5</v>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, unclassified</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2109,18 +2109,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>McKelvey Road</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
+      <c r="D23" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential, service, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -2187,14 +2187,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>3</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2213,18 +2213,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Crest Road</t>
+          <t>Struble Road</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>2</v>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary, unclassified</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Houston Road</t>
+          <t>Sevenhills Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
@@ -2265,18 +2265,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Struble Road</t>
+          <t>Crest Road</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
+      <c r="D29" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>tertiary, unclassified</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sevenhills Drive</t>
+          <t>Houston Road</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:18:35+00:00</t>
+          <t>2026-04-29T02:34:03+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:34:03+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:42:07+00:00</t>
         </is>
       </c>
     </row>
@@ -1823,18 +1823,18 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Circle Freeway</t>
+          <t>Norbourne Drive</t>
         </is>
       </c>
       <c r="C12" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D12" s="10" t="n">
-        <v>12</v>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>motorway</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1849,18 +1849,18 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Norbourne Drive</t>
+          <t>Circle Freeway</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>0</v>
+      <c r="D13" s="10" t="n">
+        <v>12</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>motorway</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1875,18 +1875,18 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Civic Center Drive</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>0</v>
+      <c r="D14" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -1927,18 +1927,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Civic Center Drive</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>2</v>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Springdale Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Springdale Road</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>McKelvey Road</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
+      <c r="D21" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>residential, service, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2109,18 +2109,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>5</v>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>McKelvey Road</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential, service, unclassified</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>3</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -2187,14 +2187,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Struble Road</t>
+          <t>Madison Avenue</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>tertiary, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2291,18 +2291,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Struble Road</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>3</v>
+      <c r="D30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>tertiary, unclassified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2343,18 +2343,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Madison Avenue</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>0</v>
+      <c r="D32" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:34:03+00:00</t>
+          <t>2026-04-29T02:42:07+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:42:07+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T02:49:19+00:00</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Springdale Road</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Springdale Road</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Adams Road</t>
+          <t>Daly Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Daly Road</t>
+          <t>Adams Road</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2057,14 +2057,14 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D21" s="10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2083,18 +2083,18 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="10" t="n">
-        <v>3</v>
+      <c r="D22" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2109,18 +2109,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
+      <c r="D23" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
+      <c r="D25" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -2187,14 +2187,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="10" t="n">
-        <v>3</v>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2213,18 +2213,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Madison Avenue</t>
+          <t>Crest Road</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
+      <c r="D27" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2239,18 +2239,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Sevenhills Drive</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>0</v>
+      <c r="D28" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2265,18 +2265,18 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Crest Road</t>
+          <t>Houston Road</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>2</v>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Struble Road</t>
+          <t>Madison Avenue</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>tertiary, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Houston Road</t>
+          <t>Sevenhills Drive</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
@@ -2343,18 +2343,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Struble Road</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>3</v>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>tertiary, unclassified</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:42:07+00:00</t>
+          <t>2026-04-29T02:49:19+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T02:49:19+00:00</t>
+          <t>Audit date (UTC): 2026-04-29T13:08:00+00:00</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Kenn Road</t>
+          <t>Springdale Road</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Springdale Road</t>
+          <t>Kenn Road</t>
         </is>
       </c>
       <c r="C18" s="5" t="n">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Daly Road</t>
+          <t>Adams Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Adams Road</t>
+          <t>Daly Road</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>McKelvey Road</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>3</v>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, unclassified</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2135,18 +2135,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>McKelvey Road</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
+      <c r="D24" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential, service, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2161,14 +2161,14 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Maple Trace</t>
+          <t>Lawnview Avenue</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>3</v>
+      <c r="D25" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -2187,14 +2187,14 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Lawnview Avenue</t>
+          <t>Maple Trace</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D26" s="5" t="n">
-        <v>0</v>
+      <c r="D26" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -2213,18 +2213,18 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Crest Road</t>
+          <t>Sevenhills Drive</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="10" t="n">
-        <v>2</v>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2239,18 +2239,18 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Houston Road</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="10" t="n">
-        <v>3</v>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Houston Road</t>
+          <t>Struble Road</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary, unclassified</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2317,18 +2317,18 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sevenhills Drive</t>
+          <t>Crest Road</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
+      <c r="D31" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2343,18 +2343,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Struble Road</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="5" t="n">
-        <v>0</v>
+      <c r="D32" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>tertiary, unclassified</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T02:49:19+00:00</t>
+          <t>2026-04-29T13:08:00+00:00</t>
         </is>
       </c>
     </row>

--- a/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
+++ b/tiger_audit_northgate_mt_healthy/reports/TIGER-Audit-Northgate-Mt-Healthy.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Audit date (UTC): 2026-04-29T13:08:00+00:00</t>
+          <t>Audit date (UTC): 2026-04-30T17:05:36+00:00</t>
         </is>
       </c>
     </row>
@@ -1875,18 +1875,18 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Civic Center Drive</t>
+          <t>Miles Road</t>
         </is>
       </c>
       <c r="C14" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="10" t="n">
-        <v>2</v>
+      <c r="D14" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Miles Road</t>
+          <t>Southland Road</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -1927,18 +1927,18 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Southland Road</t>
+          <t>Civic Center Drive</t>
         </is>
       </c>
       <c r="C16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
+      <c r="D16" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Adams Road</t>
+          <t>Daly Road</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>residential, unclassified</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Daly Road</t>
+          <t>Adams Road</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>tertiary</t>
+          <t>residential, unclassified</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2057,18 +2057,18 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>McKelvey Road</t>
+          <t>Eswin Street</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0</v>
+      <c r="D21" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>residential, service, unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2083,18 +2083,18 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Lakeview Drive</t>
+          <t>Carillon Boulevard</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D22" s="5" t="n">
-        <v>0</v>
+      <c r="D22" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>residential, tertiary</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2109,18 +2109,18 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Carillon Boulevard</t>
+          <t>Lakeview Drive</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>5</v>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, tertiary</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2135,18 +2135,18 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Eswin Street</t>
+          <t>McKelvey Road</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>3</v>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>residential, service, unclassified</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2291,18 +2291,18 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Madison Avenue</t>
+          <t>Pictoria Drive</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D30" s="5" t="n">
-        <v>0</v>
+      <c r="D30" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>unclassified</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -2343,18 +2343,18 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Pictoria Drive</t>
+          <t>Madison Avenue</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D32" s="10" t="n">
-        <v>3</v>
+      <c r="D32" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>unclassified</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -63296,7 +63296,7 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>2026-04-29T13:08:00+00:00</t>
+          <t>2026-04-30T17:05:36+00:00</t>
         </is>
       </c>
     </row>
